--- a/research/traditional_assets/database/data/israel/israel_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_insurance_prop_cas.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.05267857142857143</v>
+        <v>0.04109589041095891</v>
       </c>
       <c r="H2">
-        <v>0.05267857142857143</v>
+        <v>0.04109589041095891</v>
       </c>
       <c r="I2">
-        <v>0.1130952380952381</v>
+        <v>-0.03652968036529681</v>
       </c>
       <c r="J2">
-        <v>0.0727900202634245</v>
+        <v>-0.03652968036529681</v>
       </c>
       <c r="K2">
-        <v>2.42</v>
+        <v>-1.13</v>
       </c>
       <c r="L2">
-        <v>0.07202380952380952</v>
+        <v>-0.02579908675799087</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -621,64 +621,70 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>25.8</v>
+        <v>18.2</v>
       </c>
       <c r="V2">
-        <v>0.1800418702023726</v>
+        <v>0.4642857142857142</v>
+      </c>
+      <c r="W2">
+        <v>-0.05380952380952381</v>
       </c>
       <c r="X2">
-        <v>0.05378327415877979</v>
+        <v>0.0894741580240032</v>
+      </c>
+      <c r="Y2">
+        <v>-0.143283681833527</v>
       </c>
       <c r="AB2">
-        <v>0.05357321370005522</v>
+        <v>0.08816511978126612</v>
       </c>
       <c r="AD2">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AG2">
-        <v>-24.6</v>
+        <v>-16.89</v>
       </c>
       <c r="AH2">
-        <v>0.008304498269896193</v>
+        <v>0.03233769439644532</v>
       </c>
       <c r="AI2">
-        <v>0.05405405405405406</v>
+        <v>0.06819364914107237</v>
       </c>
       <c r="AJ2">
-        <v>-0.2072451558550969</v>
+        <v>-0.7570596145226355</v>
       </c>
       <c r="AK2">
-        <v>6.833333333333331</v>
+        <v>-16.72277227722775</v>
       </c>
       <c r="AL2">
-        <v>0.044</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AM2">
-        <v>0.044</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AN2">
-        <v>0.297029702970297</v>
+        <v>-1</v>
       </c>
       <c r="AO2">
-        <v>86.36363636363636</v>
+        <v>-18.82352941176471</v>
       </c>
       <c r="AP2">
-        <v>-6.089108910891089</v>
+        <v>12.89312977099237</v>
       </c>
       <c r="AQ2">
-        <v>86.36363636363636</v>
+        <v>-18.82352941176471</v>
       </c>
     </row>
     <row r="3">
@@ -698,22 +704,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.05267857142857143</v>
+        <v>0.04109589041095891</v>
       </c>
       <c r="H3">
-        <v>0.05267857142857143</v>
+        <v>0.04109589041095891</v>
       </c>
       <c r="I3">
-        <v>0.1130952380952381</v>
+        <v>-0.03652968036529681</v>
       </c>
       <c r="J3">
-        <v>0.0727900202634245</v>
+        <v>-0.03652968036529681</v>
       </c>
       <c r="K3">
-        <v>2.42</v>
+        <v>-1.13</v>
       </c>
       <c r="L3">
-        <v>0.07202380952380952</v>
+        <v>-0.02579908675799087</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -722,7 +728,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -731,64 +737,70 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>25.8</v>
+        <v>18.2</v>
       </c>
       <c r="V3">
-        <v>0.1800418702023726</v>
+        <v>0.4642857142857142</v>
+      </c>
+      <c r="W3">
+        <v>-0.05380952380952381</v>
       </c>
       <c r="X3">
-        <v>0.05378327415877979</v>
+        <v>0.0894741580240032</v>
+      </c>
+      <c r="Y3">
+        <v>-0.143283681833527</v>
       </c>
       <c r="AB3">
-        <v>0.05357321370005522</v>
+        <v>0.08816511978126612</v>
       </c>
       <c r="AD3">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AG3">
-        <v>-24.6</v>
+        <v>-16.89</v>
       </c>
       <c r="AH3">
-        <v>0.008304498269896193</v>
+        <v>0.03233769439644532</v>
       </c>
       <c r="AI3">
-        <v>0.05405405405405406</v>
+        <v>0.06819364914107237</v>
       </c>
       <c r="AJ3">
-        <v>-0.2072451558550969</v>
+        <v>-0.7570596145226355</v>
       </c>
       <c r="AK3">
-        <v>6.833333333333331</v>
+        <v>-16.72277227722775</v>
       </c>
       <c r="AL3">
-        <v>0.044</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AM3">
-        <v>0.044</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AN3">
-        <v>0.297029702970297</v>
+        <v>-1</v>
       </c>
       <c r="AO3">
-        <v>86.36363636363636</v>
+        <v>-18.82352941176471</v>
       </c>
       <c r="AP3">
-        <v>-6.089108910891089</v>
+        <v>12.89312977099237</v>
       </c>
       <c r="AQ3">
-        <v>86.36363636363636</v>
+        <v>-18.82352941176471</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/israel/israel_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_insurance_prop_cas.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.04109589041095891</v>
+        <v>0.01682377730952645</v>
       </c>
       <c r="H2">
-        <v>0.04109589041095891</v>
+        <v>0.01682377730952645</v>
       </c>
       <c r="I2">
-        <v>-0.03652968036529681</v>
+        <v>0.02577797493623156</v>
       </c>
       <c r="J2">
-        <v>-0.03652968036529681</v>
+        <v>0.02318426511240085</v>
       </c>
       <c r="K2">
-        <v>-1.13</v>
+        <v>7.172000000000001</v>
       </c>
       <c r="L2">
-        <v>-0.02579908675799087</v>
+        <v>0.00795386492181435</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,7 +612,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -621,70 +621,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>18.2</v>
+        <v>152.9</v>
       </c>
       <c r="V2">
-        <v>0.4642857142857142</v>
+        <v>1.638799571275455</v>
       </c>
       <c r="W2">
-        <v>-0.05380952380952381</v>
+        <v>0.01670334527401027</v>
       </c>
       <c r="X2">
-        <v>0.0894741580240032</v>
+        <v>0.1539989094610718</v>
       </c>
       <c r="Y2">
-        <v>-0.143283681833527</v>
+        <v>-0.1372955641870615</v>
+      </c>
+      <c r="Z2">
+        <v>11.4705508205063</v>
+      </c>
+      <c r="AA2">
+        <v>-0.103766151958839</v>
       </c>
       <c r="AB2">
-        <v>0.08816511978126612</v>
+        <v>0.07489596769534541</v>
+      </c>
+      <c r="AC2">
+        <v>-0.1786621196541844</v>
       </c>
       <c r="AD2">
-        <v>1.31</v>
+        <v>240.97</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.31</v>
+        <v>240.97</v>
       </c>
       <c r="AG2">
-        <v>-16.89</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.03233769439644532</v>
+        <v>0.7208843150746403</v>
       </c>
       <c r="AI2">
-        <v>0.06819364914107237</v>
+        <v>0.5903667589484775</v>
       </c>
       <c r="AJ2">
-        <v>-0.7570596145226355</v>
+        <v>0.485581959530242</v>
       </c>
       <c r="AK2">
-        <v>-16.72277227722775</v>
+        <v>0.3450072472284248</v>
       </c>
       <c r="AL2">
-        <v>0.08500000000000001</v>
+        <v>17.473</v>
       </c>
       <c r="AM2">
-        <v>0.08500000000000001</v>
+        <v>17.473</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>6.743248915628936</v>
       </c>
       <c r="AO2">
-        <v>-18.82352941176471</v>
+        <v>1.330281004979111</v>
       </c>
       <c r="AP2">
-        <v>12.89312977099237</v>
+        <v>2.464530572268084</v>
       </c>
       <c r="AQ2">
-        <v>-18.82352941176471</v>
+        <v>1.330281004979111</v>
       </c>
     </row>
     <row r="3">
@@ -695,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Libra Insurance Company Ltd (TASE:LBRA)</t>
+          <t>Wesure Global Tech Ltd (TASE:WESR)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -704,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.04109589041095891</v>
+        <v>0.01941049604601006</v>
       </c>
       <c r="H3">
-        <v>0.04109589041095891</v>
+        <v>0.01941049604601006</v>
       </c>
       <c r="I3">
-        <v>-0.03652968036529681</v>
+        <v>0.02839683680805176</v>
       </c>
       <c r="J3">
-        <v>-0.03652968036529681</v>
+        <v>0.02268241162322159</v>
       </c>
       <c r="K3">
-        <v>-1.13</v>
+        <v>7.87</v>
       </c>
       <c r="L3">
-        <v>-0.02579908675799087</v>
+        <v>0.00942966690630242</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -728,7 +737,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -737,70 +746,204 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>18.2</v>
+        <v>131.5</v>
       </c>
       <c r="V3">
-        <v>0.4642857142857142</v>
+        <v>2.981859410430839</v>
       </c>
       <c r="W3">
-        <v>-0.05380952380952381</v>
+        <v>0.07240110395584176</v>
       </c>
       <c r="X3">
-        <v>0.0894741580240032</v>
+        <v>0.2283050412246302</v>
       </c>
       <c r="Y3">
-        <v>-0.143283681833527</v>
+        <v>-0.1559039372687884</v>
+      </c>
+      <c r="Z3">
+        <v>10.75515463917525</v>
+      </c>
+      <c r="AA3">
+        <v>0.2439528445971744</v>
       </c>
       <c r="AB3">
-        <v>0.08816511978126612</v>
+        <v>0.07406751337796955</v>
+      </c>
+      <c r="AC3">
+        <v>0.1698853312192048</v>
       </c>
       <c r="AD3">
-        <v>1.31</v>
+        <v>234.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.31</v>
+        <v>234.6</v>
       </c>
       <c r="AG3">
-        <v>-16.89</v>
+        <v>103.1</v>
       </c>
       <c r="AH3">
-        <v>0.03233769439644532</v>
+        <v>0.8417653390742734</v>
       </c>
       <c r="AI3">
-        <v>0.06819364914107237</v>
+        <v>0.608402489626556</v>
       </c>
       <c r="AJ3">
-        <v>-0.7570596145226355</v>
+        <v>0.7004076086956522</v>
       </c>
       <c r="AK3">
-        <v>-16.72277227722775</v>
+        <v>0.405745769382133</v>
       </c>
       <c r="AL3">
-        <v>0.08500000000000001</v>
+        <v>17.1</v>
       </c>
       <c r="AM3">
-        <v>0.08500000000000001</v>
+        <v>17.1</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>6.498614958448753</v>
       </c>
       <c r="AO3">
-        <v>-18.82352941176471</v>
+        <v>1.385964912280702</v>
       </c>
       <c r="AP3">
-        <v>12.89312977099237</v>
+        <v>2.85595567867036</v>
       </c>
       <c r="AQ3">
-        <v>-18.82352941176471</v>
+        <v>1.385964912280702</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Libra Insurance Company Ltd (TASE:LBRA)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>-0.01535022354694486</v>
+      </c>
+      <c r="H4">
+        <v>-0.01535022354694486</v>
+      </c>
+      <c r="I4">
+        <v>-0.006795827123695977</v>
+      </c>
+      <c r="J4">
+        <v>-0.006795827123695977</v>
+      </c>
+      <c r="K4">
+        <v>-0.698</v>
+      </c>
+      <c r="L4">
+        <v>-0.01040238450074516</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>21.4</v>
+      </c>
+      <c r="V4">
+        <v>0.4349593495934959</v>
+      </c>
+      <c r="W4">
+        <v>-0.03899441340782123</v>
+      </c>
+      <c r="X4">
+        <v>0.07969277769751348</v>
+      </c>
+      <c r="Y4">
+        <v>-0.1186871911053347</v>
+      </c>
+      <c r="Z4">
+        <v>66.43564356435657</v>
+      </c>
+      <c r="AA4">
+        <v>-0.4514851485148524</v>
+      </c>
+      <c r="AB4">
+        <v>0.07572442201272128</v>
+      </c>
+      <c r="AC4">
+        <v>-0.5272095705275737</v>
+      </c>
+      <c r="AD4">
+        <v>6.37</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>6.37</v>
+      </c>
+      <c r="AG4">
+        <v>-15.03</v>
+      </c>
+      <c r="AH4">
+        <v>0.1146301961490013</v>
+      </c>
+      <c r="AI4">
+        <v>0.282233052724856</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.4398595258999121</v>
+      </c>
+      <c r="AK4">
+        <v>-12.84615384615383</v>
+      </c>
+      <c r="AL4">
+        <v>0.373</v>
+      </c>
+      <c r="AM4">
+        <v>0.373</v>
+      </c>
+      <c r="AN4">
+        <v>-17.45205479452055</v>
+      </c>
+      <c r="AO4">
+        <v>-1.222520107238606</v>
+      </c>
+      <c r="AP4">
+        <v>41.17808219178082</v>
+      </c>
+      <c r="AQ4">
+        <v>-1.222520107238606</v>
       </c>
     </row>
   </sheetData>
